--- a/pre-processing/data_cleaned/laptop.xlsx
+++ b/pre-processing/data_cleaned/laptop.xlsx
@@ -31,904 +31,904 @@
     <t>category</t>
   </si>
   <si>
+    <t>Laptop Dell Inspiron 15 3530 N3530-i3U085W11SLU (Core i3-1305U| 8GB| 512GB SSD| 15.6" FHD| Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng Tại Dell Việt Nam</t>
+  </si>
+  <si>
+    <t>Asus Vivobook 14 X1405VA-LY623W (Intel Core i5-13420H | 16GB | 512GB | 14 inch WUXGA | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>ASUS Vivobook X1404VA-NK394W (Intel Core i3-1315U | Intel UHD Graphics | 14 inch FHD | 8GB | 512GB | Win 11 Home | Bạc) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>ASUS ROG Strix G16 G614JU-N3480W (Intel Core i5-13450HX | RTX 4050 6GB | 16 inch FHD + 165Hz | 16GB | 512GB | Win 11 | Xám) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo ThinkPad E14 Gen 7 21SX002QVA (Intel Core Ultra 5 225U | 16GB | 512GB | 14 inch WUXGA | Intel Graphics | NoOS | Đen) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>MacBook Air M4 (13 inch, 16GB/ 256GB) - MW0Y3SA/A - Vàng ánh sao</t>
+  </si>
+  <si>
+    <t>Laptop Dell Inspiron 7472, Core i5-8250U, Ram 8GB, ổ cứng SSD 128GB, màn hình 14inch Full HD, VGA 2G - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 5500 Core i5-8350U, RAM 8GB, SSD 256GB - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Inspiron 7472, Core i5-8250U, Ram 8GB, SSD 128GB, 14 inch Full HD, VGA 2G - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Asus Vivobook 15 X1504ZA-NJ1039W (Intel Core i7-1255U | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>MSI Gaming Thin 15 B13UCX-2080VN (i5 13420H/ 16GB/ 512GB SSD/ RTX 2050 4GB/ 15.6 inch FHD/ 144Hz/ Win11/ Gray/ 2Y/ Balo) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop HP Gaming Victus 15-fb1023AX 94F20PA (R5 7535HS/ 8GB/ 512GB SSD/ RTX 2050 4GB/ 15.6 inch FHD/ 144Hz/ Win11/ Silver) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Máy Tính Xách Tay Laptop Samsung Galaxy Chromebook Go XE310XDA N4500/4GB/32GB/ChromeOS - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Asus Vivobook Go 15 E1504FA-NJ454W (Ryzen 5 7520U | 16GB | 512GB | 15.6 inch FHD | AMD Radeon Graphics | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop HP 15 fd1045TU 9Z2X1PA (Core 5 120U/ 16GB/ 512GB SSD/ 15.6 inch FHD/ Win11/ Bạc) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>LAPTOP HP PROBOOK 440 G10 (873B1PA) (I5 1340P/8GB RAM/512GB SSD/14 FHD CẢM ỨNG/WIN11/BẠC) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 5310 | Core i5-10310U Ram 16GB PCIe 256GB 13.3" FHD - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laptop ASUS Vivobook 15 X1504ZA i3 1215U/8GB/512GB/Win11 (NJ102W) - Hàng Chính Hãng </t>
+  </si>
+  <si>
+    <t>Máy vi tính Laptop Asus ExpertBook B1400 (Chip Intel Core i5-1235U | RAM 16GB | SSD 512GB NVMe | 14' Full HD | Bảo mật vân tay | Bảo mật TPM 2.0 | Độ bền chuẩn quân đội US) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Asus Expertbook B1502 - B1502CV (Intel Core i5-1335U | RAM 8GB | 512GB SSD | Intel UHD Graphics | 15.6 inch Full HD | Win 11 bản quyền) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Giá Rẻ Dell Vostro V3591 i3 1005G1/8GB/256GB/Intel UHD Graphics/Win 10  Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 3520 (Core i5-1135G7 | 8GB | 256GB | Intel Iris Xe | 15.6 inch FHD - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo ThinkPad X260 - Intel Core i5 6200 / Ram 8Gb / ssd 256Gb - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo Thinkpad L480 - Intel Core i5 8250U / Ram 8Gb / ssd 256gb / Màn hình 14 inch / Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkPad T460 Core i5 6200 / ram 8gb / ssd 256gb / Màn hình 14 inch- Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 3590  Core i5 7200U- Ram 8GB- 128GB SSD Ổ cứng -Màn hình 15-6 inch BH 6 thang - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Lenovo Thinkpad X250 Core i5-5200U / RAM 8GB / SSD 256GB / Màn 12.5 inch0 HD (Phím JP) Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo X1 Cacbon Core i7 / Core i5 / 16Gb / SSD nvme 256Gb Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Máy Tính Xách Tay Laptop Asus Vivobook 15 Bạc/ Intel Core i3-1315U Processor (upto 4.5Ghz, 10MB)/ RAM 8GB/ 512GB SSD/ Intel UHD Graphics/ 15.6inch FHD/ Win 11H/ 2Yrs - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Màn hình LG IPS 32MP60G-B 31.5'' Full HD AMD FreeSync - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Máy Tính Xách Tay Laptop MSI GF63 Thin 11UC-444VN (i5 11400H/8GB/512GB/15.6"FHD/NVIDIA GeForce RTX 3050 4GB/Win10_ Đen) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Máy Tính Xách Tay Màn Hình Cảm Ứng Laptop Asus VivoBook R565EA-UH51T (Core i5-1135G7, 8GB Ram, 256GB SSD, 15.6 Inch FHD Cảm ứng, Win10, Xám - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Máy tính xách tay Laptop Dell Latitude 5470  (Intel Core i5 -6200 | 14 Inch HD | RAM 8GB | 256GB SSD | Intel UHD Graphics | Fedora Os) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop LG Gram 2022 14ZD90Q-G.AX31A5 (i3-1220P | 8GB | 256GB | Intel UHD Graphics | 14' WUXGA 99% DCI-P3 | DOS) Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>(Hàng không quà tặng) Laptop LG Gram 2022 14ZD90Q-G.AX31A5-D (i3-1220P | 8GB | 256GB | Intel UHD Graphics | 14' WUXGA) Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo ThinkPad E15 Gen 4 21E600CMVA (Đen) - Tặng  chuột Zadez M-331 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP Pavilion 15-eg2058TU (6K788PA) (i5-1240P | 8GB | 256GB | Intel Iris Xe Graphics | 15.6' FHD | Win 11) Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Apple Macbook Air M2 13.6 Inch - 16GB/ 256GB - MC7W4SA/A</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 3520 70251603 (Core i3-1115G4/ 4 GB/ 256GB SSD/ 15.6HD/ Fedora) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>LapTop Lenovo V14 IIL - 82C400W3VN | Intel Core i5 _ 1035G1 | 4GB | 256GB SSD PCIe | VGA INTEL  | 14 inch HD | FreeDos | Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP Envy X360 14-fc0161TU (Core Ultra 5-125U| 16GB RAM| 512GB SSD| Intel Graphics| 14"2.8K| Blue) - Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Laptop Dell Inspiron 3530 71043887( Core i5-1334U| 8GB| 512GB SSD| Intel Iris Xe Graphics| 15.6" FHD| Đen(Black)) - Hàng Chính Hãng - Bảo Hành Chính Hãng Tại Dell Việt Nam</t>
   </si>
   <si>
-    <t>Laptop Dell Inspiron 15 3530 N3530-i3U085W11SLU (Core i3-1305U| 8GB| 512GB SSD| 15.6" FHD| Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng Tại Dell Việt Nam</t>
-  </si>
-  <si>
     <t>Asus Vivobook S 14 Flip TP3402VA-LZ632W (Intel Core i5-13420H | 16GB | 512GB | Intel UHD | 14 inch WUXGA IPS | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Asus Vivobook 15 X1502VA-BQ886W (Intel Core i7-13620H | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD IPS | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Asus Vivobook 14 X1405VA-LY623W (Intel Core i5-13420H | 16GB | 512GB | 14 inch WUXGA | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>ASUS Vivobook X1404VA-NK394W (Intel Core i3-1315U | Intel UHD Graphics | 14 inch FHD | 8GB | 512GB | Win 11 Home | Bạc) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Asus Zenbook 14 UX3405CA-PZ204WS (Intel Core Ultra 9 285H | 32GB | 1TB | Intel Arc | 14 inch 3K OLED | Cảm ứng | Win 11 | Office | Xanh) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>ASUS ROG Strix G16 G614JU-N3480W (Intel Core i5-13450HX | RTX 4050 6GB | 16 inch FHD + 165Hz | 16GB | 512GB | Win 11 | Xám) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop Asus TUF Gaming A15 FA506NCR-HN097W (R7 7435HS/ 16GB/ 512GB SSD/ RTX 3050 4GB/ 15.6 inch FHD/ 144Hz/ Win11/ Black) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo ThinkPad E14 Gen 7 21SX002QVA (Intel Core Ultra 5 225U | 16GB | 512GB | 14 inch WUXGA | Intel Graphics | NoOS | Đen) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>MacBook Air M4 (13 inch, 16GB/ 256GB) - MW0Y3SA/A - Vàng ánh sao</t>
+    <t>Dell Latitude 7390 2in1 | Core i7, RAM 16GB, SSD 512G, 13.3inch Full HD, màn cảm ứng - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5400, Core i5 8365U, RAM8GB, SSD 256GB Nvme - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Dell Precision 5540 Core i9 Ram 16gb, SSD NVME 512gb Card T2000 15.6inch IPS - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5320 Core I5 1135G7 8GB 256GB SSD 13.3 inch FHD - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5300 2in1 Core i7-8665U/Ram 8GB/SSD 256GB/13.3"FHD cảm ứng - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Laptop Lenovo V15 Gen 4 ( 83A100RGVN ) | Grey | Intel Core i7-13620H | Ram 8GB | 512GB SSD | Intel UHD Graphics | 15.6 Inch FHD | No Os | 2Yrs - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Asus Vivobook 15 X1504ZA-NJ1039W (Intel Core i7-1255U | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>MSI Gaming Thin 15 B13UCX-2080VN (i5 13420H/ 16GB/ 512GB SSD/ RTX 2050 4GB/ 15.6 inch FHD/ 144Hz/ Win11/ Gray/ 2Y/ Balo) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop HP Gaming Victus 15-fb1023AX 94F20PA (R5 7535HS/ 8GB/ 512GB SSD/ RTX 2050 4GB/ 15.6 inch FHD/ 144Hz/ Win11/ Silver) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy Tính Xách Tay Laptop Samsung Galaxy Chromebook Go XE310XDA N4500/4GB/32GB/ChromeOS - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Dell Inspiron 15 3520 25P2311 (Intel Core i5-1235U | 8GB | 512GB | Intel Iris Xe Graphics | 15.6 inch FHD | Win 11 | Office | Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
+    <t>Laptop Acer Gaming Aspire 5 A515-58GM-53CM NX.KW1SV.003 (Intel Core i5-13420H | RTX 2050 4GB | 32GB | 512GB | 15.6 inch FHD | Xám | Win 11) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop Acer Gaming Nitro Lite 16 NL16-71G-56WQ (Intel Core i5-13420H | RTX3050 | 16 inch FHD+ | 16GB | 512GB | Win 11 Home | Trắng) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop Acer Aspire 7 A715-59G-57TU NH.QX6SV.001 (Intel Core i5-12450H | RTX 3050 | 15.6 inch FHD | 16GB | 512GB | Win 11 | Đen) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5510 Core i5-10310U Ram 16GB SSD 256GB 15.6 inch FHD - Hàng Chính hãng</t>
+  </si>
+  <si>
+    <t>LAPTOP HP 240 G9 AG2J7AT( i5-1235U/ 16GD4 /512GSSD/ 14.0FHD/ WLax/ BT5/ 3C41WHr/W11SL/BẠC ) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>[Laptop I5-13420H] Laptop Asus Expertbook P1403CVA (Intel Core i5-13420H | 14 inch FHD IPS | RAM 16GB | SSD 512GB | Win bản quyền)</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo V14 Gen 4 IRU 83A000BEVN i5-13420H | 8GB | 512GB | 14' FHD | Win 11 - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>MSI Thin 15 B12UC-1416VN (Intel Core i5-12450H | RTX 3050 4GB | 15.6 inch FHD | 8GB | Win 11 | Xám) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
     <t>Laptop Asus Zenbook S 14 OLED UX5406SA-PV140WS (Intel Core Ultra 7 Processor 258V | 14 inch 3K OLED | Intel Arc | 32GB | 1TB | Win 11 | Office |Trắng) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Laptop ASUS Vivobook 15 OLED A1505VA-L1341W (Core i5-13500H | 16GB | 512GB | Intel Iris Xᵉ | 15.6inch FHD OLED | Win 11 | Đen) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop HP 15 fd1045TU 9Z2X1PA (Core 5 120U/ 16GB/ 512GB SSD/ 15.6 inch FHD/ Win11/ Bạc) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>LAPTOP HP PROBOOK 440 G10 (873B1PA) (I5 1340P/8GB RAM/512GB SSD/14 FHD CẢM ỨNG/WIN11/BẠC) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laptop ASUS Vivobook 15 X1504ZA i3 1215U/8GB/512GB/Win11 (NJ102W) - Hàng Chính Hãng </t>
-  </si>
-  <si>
-    <t>Máy vi tính Laptop Asus ExpertBook B1400 (Chip Intel Core i5-1235U | RAM 16GB | SSD 512GB NVMe | 14' Full HD | Bảo mật vân tay | Bảo mật TPM 2.0 | Độ bền chuẩn quân đội US) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Acer Aspire A314 42P R3B3 NX.KSFSV.001 (Ryzen 7 5700U/ 16GB/ 512GB SSD/ AMD Radeon Graphics/ 14.0inch Full HD+/ Windows 11 Home/ Silver/ 1 Year) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
+    <t>Laptop LG Gram 2024 17Z90S-G.AH78A5 (Intel Core Ultra 7 155H | 16GB | 1TB | Intel Arc | 17 inch WQXGA | Win 11 | Đen) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
+  </si>
+  <si>
+    <t>Lenovo Thinkpad T480 Core i5-8250U / RAM 16GB / SSD 256GB / Màn 14.0 inch FHD 1920x1080 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP 15 fd1043TU 9Z2W9PA (Core 5 120U/ 16GB/ 1TB SSD/ 15.6 inch FHD/ Win11/ Bạc) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP EliteBook 630 G10 9J0B3PT (i5 1335U/ 8GB/ 512GB SSD/13.3 inch FHD/Win11/ Silver/ Vỏ nhôm) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 7430 CTO-14"FHD/i5-1235U/8Gb/M.2 256Gb/Win10Pro/3YPro - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Vostro 5370 (i5-8250U/ Ram 8GB/ SSD 256GB/ 13.3"FHD /Sliver/ W10/FG/Key_led) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
     <t>Laptop MSI Katana 15 B13VFK 676VN | CPU i7-13620H | RAM 16GB DDR5 | SSD 1TB PCle | VGA RTX 4060 8GB | 15.6 FHD IPS 144Hz | Win11 - Hàng Chính Hãng - Bảo Hành 24 Tháng</t>
   </si>
   <si>
-    <t>Laptop Asus Expertbook B1502 - B1502CV (Intel Core i5-1335U | RAM 8GB | 512GB SSD | Intel UHD Graphics | 15.6 inch Full HD | Win 11 bản quyền) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Asus Vivobook Go 14 E1404FA-NK177W (Ryzen 5 7520U | 16GB | 512GB | 14 inch FHD | AMD Radeon Graphics | Win 11 | Bạc) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy Tính Xách Tay Laptop Asus Vivobook 15 Bạc/ Intel Core i3-1315U Processor (upto 4.5Ghz, 10MB)/ RAM 8GB/ 512GB SSD/ Intel UHD Graphics/ 15.6inch FHD/ Win 11H/ 2Yrs - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Màn hình LG IPS 32MP60G-B 31.5'' Full HD AMD FreeSync - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo IdeaPad Gaming 3 15ARH7 82SB007MVN | AMD Ryzen 7 6800H | 16GB | 512GB SSD | RTX 3050 Ti 4GB | 15.6 inch Full HD IPS 120Hz | Win 11 | LED KEY RGB | Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Máy Tính Xách Tay Laptop Asus Zenbook Q409ZA-EV0.I5256BL ( Intel Core i5.1240P/8GB LPDDR4/SSD 256GB/Intel Iris Xe Graphics/14inch OLED WQ/Win11/Blue ) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy Tính Xách Tay Laptop MSI GF63 Thin 11UC-444VN (i5 11400H/8GB/512GB/15.6"FHD/NVIDIA GeForce RTX 3050 4GB/Win10_ Đen) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy Tính Xách Tay Màn Hình Cảm Ứng Laptop Asus VivoBook R565EA-UH51T (Core i5-1135G7, 8GB Ram, 256GB SSD, 15.6 Inch FHD Cảm ứng, Win10, Xám - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2022 14ZD90Q-G.AX31A5 (i3-1220P | 8GB | 256GB | Intel UHD Graphics | 14' WUXGA 99% DCI-P3 | DOS) Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>(Hàng không quà tặng) Laptop LG Gram 2022 14ZD90Q-G.AX31A5-D (i3-1220P | 8GB | 256GB | Intel UHD Graphics | 14' WUXGA) Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo ThinkPad E15 Gen 4 21E600CMVA (Đen) - Tặng  chuột Zadez M-331 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP Pavilion 15-eg2058TU (6K788PA) (i5-1240P | 8GB | 256GB | Intel Iris Xe Graphics | 15.6' FHD | Win 11) Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Apple Macbook Air M2 13.6 Inch - 16GB/ 256GB - MC7X4SA/A</t>
-  </si>
-  <si>
-    <t>Laptop Dell Latitude 3520 70251603 (Core i3-1115G4/ 4 GB/ 256GB SSD/ 15.6HD/ Fedora) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>LapTop Lenovo V14 IIL - 82C400W3VN | Intel Core i5 _ 1035G1 | 4GB | 256GB SSD PCIe | VGA INTEL  | 14 inch HD | FreeDos | Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP Envy X360 14-fc0161TU (Core Ultra 5-125U| 16GB RAM| 512GB SSD| Intel Graphics| 14"2.8K| Blue) - Hàng Chính Hãng</t>
+    <t>DELL LATITUDE E3510 (I5-102104U/ RAM 16GB/ 256GB SSD NVME/ 15.6 INCH FULL HD) Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Latitude 3410 (L3410I5SSD) (i5 10210U 8GB RAM/256GB SSD/14.0 inch HD/Fedora/Xám) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>LAPTOP LENOVO X1 CARBON GEN 4/ CORE I5-6300U / RAM 8GB / SSD 512GB / MÀN HÌNH 14 INCH / HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>LAPTOP Thinkpad X1 Carbon Gen 6 | I7 – 8550U | Ram 16GB | SSD 512GB | 14″ Full HD | Card On</t>
+  </si>
+  <si>
+    <t>Laptop Asus Vivobook 15 (X1504VA-NJ069W) / Bạc/ Intel Core i3-1315U Processor (upto 4.5Ghz, 10MB)/ RAM 8GB/ 512GB SSD/ Intel UHD Graphics/ 15.6inch FHD/ Win 11H/ 2Yrs - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop LG Gram 2022 14ZD90Q-G.AX32A5 (Intel Core i3-1220P/8GB/256GB/VGA Intel UHD Graphics/14 inch WQXGA/Màu Đen/Non- OS)- Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop LG Gram 2022 14Z90Q-G.AJ32A5 (i3-1220P | 8GB | 256GB | Intel UHD Graphics | 14' WUXGA 99% DCI-P3 | Win 11) Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop LG Gram 2021 17Z90P-G.AH76A5 i7-1165G7 | 16GB | 512GB | Intel Iris Xe Graphics | 17' WQXGA | Win 10 Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Laptop Asus VivoBook X515JA Core i3-1005G1/8GB/256GB/15.6"HD/Win 10/Màu Xám Mới 100%-Hàng Nhập Khẩu</t>
+  </si>
+  <si>
+    <t>Lenovo Thinkpad X1 Carbon Thế Hệ 5 Core i5 – 7300U / Ram 8G / SSD 256Gb / 14 “FHD / SIÊU MỎNG - SIÊU NHANH - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkPad L460 (Intel Core i5 6300 , RAM 8.0GB, 1x180GB SSD SATA III, Intel HD 520, MÀN HÌNH 14 INCH Tặng cặp + chuột không dây + bàn di chuột - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Laptop MSI Modern 14 B11SBU 668VN Carbon Gray (i5 1155G7/ 8GB/ 512GB SSD/ MX450 2GB/ W10) Hàng NK</t>
+  </si>
+  <si>
+    <t>Laptop MSI Modern 14 B11MOU 851VN Gray (i3 1115G4/ 8GB/ 256GB SSD/ W10) Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP 14s-fq1080AU 4K0Z7PA (AMD R3-5300U/ 4GB DDR4/ 256GB SSD/ 14 HD/ Win 11) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop LG Gram 2021 17Z90P-G.AH78A5 (Core i7-1165G7/ 16GB LPDDR4X/ 1TB SSD NVMe/ 17 WQXGA IPS/ Win10) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Asus Expertbook P1403CVA (Intel Core i3-1335U | 14 inch FHD IPS | RAM 8GB | SSD 256GB | Win bản quyền) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Lenovo ThinkPad E14 Gen 6 (21M7004XVA) | Ultra 7 155H | 16GB | 1TB | NPU 11 TOPS | 14 inch WUXGA | IPS | Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop Dell Inspiron 15 3520 71069202 ( Core i7-1255U| 16GB| 512GB SSD| Intel Iris Xe Graphics| 15.6" FHD| Đen) - Hàng Chính Hãng - Bảo Hành 12 Tháng tại Dell Việt Nam</t>
+  </si>
+  <si>
+    <t>Laptop Dell Inspiron 15 3520 71058652 ( i5-1235U| 8GB| 512GB SSD| 15.6" FHD|  Bạc (Platinum Silver))  - Hàng Chính Hãng - Bảo Hành 12 Tháng tại Dell Việt Nam</t>
+  </si>
+  <si>
+    <t>Dell Inspiron 3530  71053696( Core i5-1334U| 16GB| 512GB SSD| Intel Iris Xe Graphics| 15.6" FHD| Bạc (Platinum Silver)) - Hàng Chính Hãng- Bảo Hành 12 Tháng Tại Dell Việt Nam</t>
+  </si>
+  <si>
+    <t>Laptop Dell Inspiron 15 3520 N3520-i5U085W11SLU( Core i5-1235U| 8GB| 512GB SSD| 15.6" FHD| Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng Tại Dell Việt Nam</t>
+  </si>
+  <si>
+    <t>Asus Vivobook 15 X1504VA-NJ1969W (Intel Core i5-1334U | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD IPS | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
     <t>Asus Vivobook 15 A1505V-L1688W (Intel Core i7-13620H | 16GB | 512GB | Intel UHD | 15.6 inch FHD | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
+    <t>ASUS ExpertBook B1 B1403CTA-S60046W (i3-N355 | Ram 8Gb DDR5 | SSD 256GB | Màn hình 14 FHD | Win 11 | Xám) - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
     <t>Asus Vivobook 15 X1504VA-BQ2076W (Intel Core i5-1334U | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD IPS | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Laptop Acer Gaming Aspire 5 A515-58GM-53CM NX.KW1SV.003 (Intel Core i5-13420H | RTX 2050 4GB | 32GB | 512GB | 15.6 inch FHD | Xám | Win 11) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop Acer Gaming Nitro Lite 16 NL16-71G-56WQ (Intel Core i5-13420H | RTX3050 | 16 inch FHD+ | 16GB | 512GB | Win 11 Home | Trắng) - HÀNG CHÍNH HÃNG</t>
+    <t>Dell Inspiron 14 Plus 7440 - Intel Core i5-12450H  Ram 16GB  SSD 512GB 14 inch FullHD + 250nits  Iced Blue - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Laptop Acer Aspire 7 A715-59G-73LB NH.QX6SV.002 (Intel Core i7-12650H | RTX 3050 6GB | 15.6 inch FHD IPS 144Hz | 16GB | 512GB | Win 11 | Đen) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Laptop Acer Aspire 7 A715-59G-57TU NH.QX6SV.001 (Intel Core i5-12450H | RTX 3050 | 15.6 inch FHD | 16GB | 512GB | Win 11 | Đen) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>LAPTOP HP 240 G9 AG2J7AT( i5-1235U/ 16GD4 /512GSSD/ 14.0FHD/ WLax/ BT5/ 3C41WHr/W11SL/BẠC ) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>[Laptop I5-13420H] Laptop Asus Expertbook P1403CVA (Intel Core i5-13420H | 14 inch FHD IPS | RAM 16GB | SSD 512GB | Win bản quyền)</t>
-  </si>
-  <si>
-    <t>Laptop Acer Aspire Lite 15 AL15 41P R3QL R7 5700U/8GB/512GB/Win11 (NX.J54SV.001) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo V14 Gen 4 IRU 83A000BEVN i5-13420H | 8GB | 512GB | 14' FHD | Win 11 - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
     <t>Laptop HP ProBook 440 G10 9H8U4PT (i5 1335U/ 8GB/ 512GB SSD/14 inch FHD/Win11/ Silver/ Vỏ nhôm) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
     <t>Laptop HP ProBook 450 G9 6M0Y5PA (i3 1215U/ 8GB/ 512GB SSD/15.6 inch/Win11/ Silver) - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>MSI Thin 15 B12UC-1416VN (Intel Core i5-12450H | RTX 3050 4GB | 15.6 inch FHD | 8GB | Win 11 | Xám) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2024 17Z90S-G.AH78A5 (Intel Core Ultra 7 155H | 16GB | 1TB | Intel Arc | 17 inch WQXGA | Win 11 | Đen) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
+    <t>Dell Latitude 5410 /Core i5-10310U / RAM 8GB / SSD 256GB / 14inch FHD - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Laptop LG Gram 2024 14Z90S-G.AH75A5 (Intel Core Ultra 7 155H |16GB | 512GB | Intel Arc | 14 inch WUXGA | Win11 | Đen) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
   </si>
   <si>
-    <t>Laptop Asus Vivobook 15 OLED A1505VA-MA468W (Intel Core i5-13500H | 16GB | 512GB | Intel Iris Xe | 15.6 inch 2.8K | Win 11 | Đen) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop Asus Vivobook Go 15 E1504FA-NJ454W (Ryzen 5 7520U | 16GB | 512GB | 15.6 inch FHD | AMD Radeon Graphics | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop HP 15 fd1043TU 9Z2W9PA (Core 5 120U/ 16GB/ 1TB SSD/ 15.6 inch FHD/ Win11/ Bạc) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP EliteBook 630 G10 9J0B3PT (i5 1335U/ 8GB/ 512GB SSD/13.3 inch FHD/Win11/ Silver/ Vỏ nhôm) - Hàng Chính Hãng</t>
+    <t>Lenovo Thinkpad T480 Core i7 8550U / RAM 16GB / SSD 256GB / Màn 14.0 inch FHD 1920x1080 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP Pavilion 15-eg3091TU 8C5L2PA (i7 1355U/ 16GB/ 512GB SSD/15.6 inch FHD/Win11/ Gold/ Vỏ nhôm) - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Laptop HP Envy X360 14-fc0091TU (A19C1PA) (Ultra5 125U/16GB RAM/1TB SSD/14 2.8K Cảm ứng/Bút/Win11/Xanh) - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Laptop Gaming Acer Nitro V ANV15-51-55CA NH.QN8SV.004 (Intel Core i5-13420H | RTX 4050 6GB | 16GB | 512GB | 15.6 inch FHD | Win 11 | Đen) - HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
-    <t>Laptop HP 15-fd0235TU 9Q970PA (Intel Core i5-1334U | 16GB | 512GB | Iris Xe Graphics | 15.6 inch FHD | Windows 11 | Natural silver) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
-  </si>
-  <si>
-    <t>Máy tính xách tay Acer N22Q25 (A515-58GM-53PZ) (i5-13420H;8GB; 512GB SSD; RTX2050/4GB;15.6" FHD; Win11; Xám;NX.KQ4SV.008) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop Dell Latitude 7430 CTO-14"FHD/i5-1235U/8Gb/M.2 256Gb/Win10Pro/3YPro - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP Pavilion 15-eg3093TU 8C5L4PA (Core i5-1335U | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD | Windows 11 | Vàng) - Hàng Chính Hãng - Bảo Hành 12 Tháng Tại HP Việt Nam</t>
-  </si>
-  <si>
-    <t>Laptop Dell Vostro 3430 (V3430-i7U165W11GRD2) |Core i7 _ 1355U | 16GB | 512GB SSD PCIe |MX550 2GB| 14 inch Full HD IPS | Win 11 _ Office 2021| Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Asus Vivobook 15 (X1504VA-NJ069W) / Bạc/ Intel Core i3-1315U Processor (upto 4.5Ghz, 10MB)/ RAM 8GB/ 512GB SSD/ Intel UHD Graphics/ 15.6inch FHD/ Win 11H/ 2Yrs - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2022 14ZD90Q-G.AX32A5 (Intel Core i3-1220P/8GB/256GB/VGA Intel UHD Graphics/14 inch WQXGA/Màu Đen/Non- OS)- Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Máy Tính Xách Tay Laptop LG Gram 14Z90P-G.AH75A5 Core i7-1165G7/ RAM 16GB 4266MHz/ M.2(2280) Dual SSD slots - NVME:  512GB/ Intel Iris Xe Graphics / 14.0"(30.2cm) WUXGA (1920*1200) IPS/ / BT 5.1/ Pin 72WHrs/ Obsidian Black/ Win 10/ 999g - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2022 14ZD90Q-G.AX56A5 (i5-1240P | 16GB | 512GB | Intel Iris Xe Graphics | 14' WUXGA 99% DCI-P3 | DOS) Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2022 14Z90Q-G.AJ32A5 (i3-1220P | 8GB | 256GB | Intel UHD Graphics | 14' WUXGA 99% DCI-P3 | Win 11) Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2021 17Z90P-G.AH76A5 i7-1165G7 | 16GB | 512GB | Intel Iris Xe Graphics | 17' WQXGA | Win 10 Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG gram 14'', Không hệ điều hành, Intel Core i3 Gen 12, 8Gb, 256GB, 14ZD90Q-G.AX32A5 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Asus Vivobook F415E i3-1115G4/8GB/128SSD/UHD Graphics/14"FHD/Win10/Xám Mới 100%- Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>Laptop Asus VivoBook X515JA Core i3-1005G1/8GB/256GB/15.6"HD/Win 10/Màu Xám Mới 100%-Hàng Nhập Khẩu</t>
-  </si>
-  <si>
-    <t>Laptop Asus Vivobook 15 R565EA UH51T (I5-1135G7/ 8G/ 256GB PCIE/ 15.6 FHD/ CẢM ỨNG/ WIN10/ XÁM) - Hàng Nhập Khẩu Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop MSI Modern 14 B11SBU 668VN Carbon Gray (i5 1155G7/ 8GB/ 512GB SSD/ MX450 2GB/ W10) Hàng NK</t>
-  </si>
-  <si>
-    <t>Laptop MSI Modern 14 B11MOU 851VN Gray (i3 1115G4/ 8GB/ 256GB SSD/ W10) Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP 14s-fq1080AU 4K0Z7PA (AMD R3-5300U/ 4GB DDR4/ 256GB SSD/ 14 HD/ Win 11) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2021 17Z90P-G.AH78A5 (Core i7-1165G7/ 16GB LPDDR4X/ 1TB SSD NVMe/ 17 WQXGA IPS/ Win10) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo ThinkPad E14 Gen 6 (21M7004XVA) | Ultra 7 155H | 16GB | 1TB | NPU 11 TOPS | 14 inch WUXGA | IPS | Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop Dell Inspiron 15 3520 71069202 ( Core i7-1255U| 16GB| 512GB SSD| Intel Iris Xe Graphics| 15.6" FHD| Đen) - Hàng Chính Hãng - Bảo Hành 12 Tháng tại Dell Việt Nam</t>
-  </si>
-  <si>
-    <t>Laptop Dell Inspiron 15 3520 N5I5003W1 (Core i5 - 1235U| 8Gb| 512Gb SSD NVMe| 15.6" FHD 1920 x 1080| BLACK) - Hàng Chính Hãng - Bảo Hành 12 Tháng tại Dell Việt Nam</t>
-  </si>
-  <si>
-    <t>Laptop Dell Inspiron 15 3520 71058652 ( i5-1235U| 8GB| 512GB SSD| 15.6" FHD|  Bạc (Platinum Silver))  - Hàng Chính Hãng - Bảo Hành 12 Tháng tại Dell Việt Nam</t>
-  </si>
-  <si>
-    <t>Dell Inspiron 3530  71053696( Core i5-1334U| 16GB| 512GB SSD| Intel Iris Xe Graphics| 15.6" FHD| Bạc (Platinum Silver)) - Hàng Chính Hãng- Bảo Hành 12 Tháng Tại Dell Việt Nam</t>
-  </si>
-  <si>
-    <t>Laptop Dell Inspiron 15 3520 N3520-i5U085W11SLU( Core i5-1235U| 8GB| 512GB SSD| 15.6" FHD| Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng Tại Dell Việt Nam</t>
-  </si>
-  <si>
-    <t>Asus Vivobook 15 X1504VA-NJ1969W (Intel Core i5-1334U | 16GB | 512GB | Intel Iris Xe | 15.6 inch FHD IPS | Win 11 | Bạc) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>ASUS ExpertBook B1 B1403CTA-S60046W (i3-N355 | Ram 8Gb DDR5 | SSD 256GB | Màn hình 14 FHD | Win 11 | Xám) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Laptop HP Pavilion 15-eg3091TU 8C5L2PA (i7 1355U/ 16GB/ 512GB SSD/15.6 inch FHD/Win11/ Gold/ Vỏ nhôm) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP Envy X360 14-fc0091TU (A19C1PA) (Ultra5 125U/16GB RAM/1TB SSD/14 2.8K Cảm ứng/Bút/Win11/Xanh) - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Laptop HP 14 - ep0112TU 8C5L1PA (Intel Core i5-1335U | 16GB | 512GB | Intel Iris Xe | 14 inch FHD | Win 11 | Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng</t>
-  </si>
-  <si>
-    <t>MÁY TÍNH XÁCH TAY (NB) ACER Aspire 7 A715-76-53PJ i5-12450H/16GD4/512SSD_PCIe/15.6FHD/FP/IPS/4C/W11SL/ĐEN(NH.QGESV.007) - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Lenovo ThinkPad E16 Gen 3 (21SR002JVA) | Intel Core Ultra 5 225U | 16GB | 512GB | Intel Graphics | 16.0 inch WUXGA | No OS | Black | AI PC</t>
-  </si>
-  <si>
-    <t>Laptop HP Pavilion 15-eg2083TU 7C0W9PA (Core i5-1240P | 8GB | 512GB | Intel Iris Xe | 15.6 inch FHD IPS | Win 11 | Bạc) - Hàng Chính Hãng - Bảo Hành 12 Tháng Tại HP Việt Nam</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo ThinkPad E14 Gen 6 (21M7004WVA) | Intel Ultra 7 155H | 16GB | 512GB | Intel® Arc™ Graphics | 14inch WUXGA | No OS | Đen</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo V15 G4 IRU (83A100URVN) | Intel Core i5-13420H | 8GB | 512GB SSD | Intel UHD Graphics | 15.6 Inch FHD | No Os | Grey</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo V14 Gen 4 (83A000FNVN) | Intel Core I5-13420H | 16GB | 512GB | 14.0" FHD | NO OS | Grey</t>
-  </si>
-  <si>
-    <t>Laptop LG Gram 2022 14ZD90Q-G.AX56A5 (Core i5-1240P/16GB /512GB/ Iris Xe Graphics/14 inch WUXGA/ Non-OS/ Grey)- Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Laptop Lenovo ThinkPad E14 Gen 7 (21SX002QVA) | Intel Core Ultra 5 225U | RAM 16GB | 512GB SSD | Intel Graphics | 14 inch WUXGA | Fingerprint | WF+BL | 3 cell | NoOS | 2Yrs</t>
-  </si>
-  <si>
-    <t>Laptop Dell Inspiron 5620 | N5620 - I5P165W11SLU (Intel Core i5 _ 1240P | 16GB | 512GB SSD | Intel Iris Xe  | 16.0 inch Full HD+ | Win 11 _ Office 2021 | Finger | LED KEY ) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278226869.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278226504.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078317.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078298.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078286.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078281.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078278.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278076611.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278076601.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278071899.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277991695.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277912853.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277451016.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277363552.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277361314.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276378910.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276370396.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276366370.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276366073.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275854386.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275382480.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275269577.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_274643985.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_274419342.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_274378954.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_273949286.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_272828266.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_252566514.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_248830867.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_247666447.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_247656002.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_225195616.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_225195387.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_214863390.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_214863343.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_206840788.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_206307542.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_189371737.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_108924121.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_67982880.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278229740.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078311.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278076593.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277912740.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277912721.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277912717.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277912715.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277672516.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277466579.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277462473.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277446629.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277363548.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_277361271.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276603695.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276366329.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276366221.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276366080.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_276365829.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275854376.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275850110.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275746519.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275721993.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275382529.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275154280.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_273647623.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_273231142.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_252566338.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_225934432.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_225363237.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_214863401.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_214863371.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_214863351.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_198437064.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_189572223.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_189572199.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_160445997.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_158583221.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_158583026.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_155974507.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_92621126.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278454662.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278304793.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278304363.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278304303.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278227010.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278226626.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278078315.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_278076596.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275852844.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275850187.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275516477.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_275381290.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_274775419.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_273634022.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_273239856.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_271949876.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_247667322.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_225940640.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_205305968.jpg</t>
-  </si>
-  <si>
-    <t>images/laptop/product_205303070.jpg</t>
+    <t>images/laptop/278226504.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278078286.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278078281.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278076611.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278071899.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277991695.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277961929.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277953961.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277936690.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277451016.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277363552.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277361314.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/276378910.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/276365829.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/275854386.png</t>
+  </si>
+  <si>
+    <t>images/laptop/275382480.png</t>
+  </si>
+  <si>
+    <t>images/laptop/275288865.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/275269577.png</t>
+  </si>
+  <si>
+    <t>images/laptop/274643985.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273949286.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/273747303.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273679076.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273309458.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/273187662.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273186974.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273002756.png</t>
+  </si>
+  <si>
+    <t>images/laptop/271264846.png</t>
+  </si>
+  <si>
+    <t>images/laptop/270837635.png</t>
+  </si>
+  <si>
+    <t>images/laptop/252566514.png</t>
+  </si>
+  <si>
+    <t>images/laptop/248830867.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/225195616.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/225195387.png</t>
+  </si>
+  <si>
+    <t>images/laptop/222707075.png</t>
+  </si>
+  <si>
+    <t>images/laptop/214863390.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/214863343.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/206840788.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/206307542.png</t>
+  </si>
+  <si>
+    <t>images/laptop/189371737.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/108924121.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/67982880.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278229740.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278226869.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278078317.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277961884.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277952237.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277945130.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277937199.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277936146.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277912853.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277912740.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277912721.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277912715.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277908157.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277672516.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277466579.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277446629.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/276603695.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/276366370.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/276366329.png</t>
+  </si>
+  <si>
+    <t>images/laptop/276026379.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/275854376.png</t>
+  </si>
+  <si>
+    <t>images/laptop/275850110.png</t>
+  </si>
+  <si>
+    <t>images/laptop/275154280.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/274734984.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/274378954.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273747677.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/273679080.png</t>
+  </si>
+  <si>
+    <t>images/laptop/273329318.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/253096916.png</t>
+  </si>
+  <si>
+    <t>images/laptop/252566338.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/225934432.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/214863371.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/214863351.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/189572199.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/186272654.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/183743642.png</t>
+  </si>
+  <si>
+    <t>images/laptop/158583221.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/158583026.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/155974507.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/92621126.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278588312.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278454662.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278304793.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278304303.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278227010.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278226626.png</t>
+  </si>
+  <si>
+    <t>images/laptop/278078315.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278078311.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278076596.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/278076593.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277937155.png</t>
+  </si>
+  <si>
+    <t>images/laptop/277912717.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277363548.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277361271.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/277274848.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/276366221.png</t>
+  </si>
+  <si>
+    <t>images/laptop/276026443.jpg</t>
+  </si>
+  <si>
+    <t>images/laptop/275852844.png</t>
+  </si>
+  <si>
+    <t>images/laptop/275850187.png</t>
+  </si>
+  <si>
+    <t>images/laptop/275746519.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/19/45/01/756b81b05d11f581c1de67ccb060a5ce.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/05/f5/278114b98bc60cdfdfdeceef4b732ee7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/08/be/2d/bd74e4abe49f7d0d7e9a6d25805e4d29.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f8/87/67/57f14f630ffeb6fbae41e3ba2f1c5578.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/64/b9/72/be26f09b48baf945722af7332c59594c.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/18/87/1d/c8af09a5551e281048c10550999ed742.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7f/f9/95/9895933f6c561e0c9a33c4678143974a.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ae/e0/5f/9381b2b83c14e8cb8f3e542680f3abe4.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7f/f9/95/5f434e119bf372f4e500c52703fe067f.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1a/f5/fd/9ca2b31247c9923acdfc0f929f8fcadc.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/03/ba/ed/c99a74f8ec15b3adf72261dd3d78d733.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4b/9a/14/6d85321b51777511d7bb0eb98008cf72.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/14/83/c2/c33a5b55b19354eb7f712f36aff5b76e.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/17/4c/f8/4845fd322e80b270b7f1a21f9b65da76.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/17/93/c9/92ea6fef866fb2a67c549c959384cdf3.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7a/8c/49/769235be295bc27dc8dca20f664bb5b1.jpeg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/20/0b/e3/18771f52e2f1fdcc36ce119db9fa660d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b7/ff/65/e919c1be4ff68b0a6633c7b9730c4da8.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/61/07/31ed28cfaca4174838bf1eac0744dd8b.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c3/38/e0/78676b0c573733c58a097aaa70a97d37.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7a/a7/a3/4e5636f9abdeb54984dd7707fa3e6e93.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/25/db/e4/f439e2d0248760a550b46af11677ce85.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/94/a6/2c/f485f6bc6bd10f93eeba04607c11a402.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/12/54/b724bf19c230b9dd3687c9e830c871e2.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/12/54/2292f44fd15197f0ef0de28c37506fd8.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/88/ff/11/c0e2995f65ed406e3e4ba54e17c32692.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1b/37/d6/a2bbbda4b2f46acbc3fee1c79089a614.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/72/8d/fa/c3ae8a33feb34eee250219ffc769775f.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/8c/a8/09b97e025f344d0e0d05245926f65ba6.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b0/fd/be/68e480053bf68493232c75df86b66978.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/14/2c/31fa634784e91004778549ee9f7915a9.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/b7/8b/7bd87c7e4ce32d719b9a55391d746ad7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b7/0e/f1/10ebb987c4bb70d4ff1169fb56c77a67.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/4f/c1/f6e0f64980bc4f9cd51a23eba78c3cba.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ec/42/56/cb83392c7e5091d9faeca52cd29348c5.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a7/ae/3a/d7aaa7c0bae2a1059d79e9d7870006af.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3f/a6/a4/140ce4c6780c706edcfdcabcf61950b0.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/media/catalog/producttmp/1a/7f/72/5f3c9a7499bc976b932ef8cbd58c0282.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/a8/e0/0fabf09e71ac203abefa2d19dc473ca7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/db/b5/11/9b49a332d68f5f3e77ba0cd203e4da60.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/89/5f/7b/77661c5bc169a60097c58e905ea983cd.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/5a/a1/bf/fc1a072b745d181d04d6a47b5641a944.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/19/45/01/756b81b05d11f581c1de67ccb060a5ce.png</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/16/9c/8966ab408a3b93acba7e948b5ab5e4aa.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/12/49/d9/d1807785da56bf01f1db44069bbc1310.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/05/f5/278114b98bc60cdfdfdeceef4b732ee7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/08/be/2d/bd74e4abe49f7d0d7e9a6d25805e4d29.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/22/f9/a4/2d61d34898c39395c8e174422bdf05c0.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f8/87/67/57f14f630ffeb6fbae41e3ba2f1c5578.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6a/c5/36/786deee9303e3befa251b429d90f70b3.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/64/b9/72/be26f09b48baf945722af7332c59594c.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/18/87/1d/c8af09a5551e281048c10550999ed742.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b0/7d/13/913343d953acbe97d4330b758a01e78a.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/03/28/67/4779589816d8cc811c0437d2e5c7170a.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e8/ee/38/7bbad1bb333cef5ec45a6981e9261659.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/79/2e/4d/cb2bd2d53e7a01ccba5563d06f862c61.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/51/c8/52/732c429c1f0c21f14966854484e9b690.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/3a/1e/b0/d5aa10dc19cb272d259cbcff9a3779e1.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1a/f5/fd/9ca2b31247c9923acdfc0f929f8fcadc.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/03/ba/ed/c99a74f8ec15b3adf72261dd3d78d733.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4b/9a/14/6d85321b51777511d7bb0eb98008cf72.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/14/83/c2/c33a5b55b19354eb7f712f36aff5b76e.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5b/92/00/65c185a546f7240f55651e112b6fc44f.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/65/83/e1/43688269800cd87d7b13b2fc04bd7a4a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/65/eb/8f/605a790fe74b2edc8b97373c955f0674.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/19/e2/f5b790ba517f48f43f88f711a93ba492.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/dd/ae/6d/a7dd0fedd087ad775d4aa7196ae20a91.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/53/2f/9f/bfecd76a1ebfe0b7657dc2fe74079fd8.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/49/de/6c/eff4593d00ec470babc53f8647457e0f.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/74/aa/bc/5a87679708539a7edf488f20ac9e5c58.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/89/09/1a/2f279301e492a813f79570dda97f3231.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/52/17/a2/91d7ee27a62001c7849377aa97a8ec1a.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/27/92/11/c124646849b2f0ebc94443f4bae33379.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/17/93/c9/92ea6fef866fb2a67c549c959384cdf3.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7a/8c/49/769235be295bc27dc8dca20f664bb5b1.jpeg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b7/ff/65/e919c1be4ff68b0a6633c7b9730c4da8.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/61/07/31ed28cfaca4174838bf1eac0744dd8b.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/88/bc/e7/7c6c09e33dca2ac63f19c85e06ce940c.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/08/76/a5/de3fb3d1d1fc711156c60fb4616a2f63.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/81/77/f8/a51cc25e4beb6372294b3d678f02d444.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0b/b5/88/7a745e1be60d35000868ec8e99ab96ae.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ac/ed/15/c7847e98527242dba0721bbb18cfeb8c.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/c2/71/0218ffcde5582b38502c8a2f5ebad629.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/b2/47/4c8604ed45f2e8668e219508e918ba4f.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/3b/c5/a3/390d6035c1b752425f693d431ca9a42e.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c3/38/e0/78676b0c573733c58a097aaa70a97d37.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/85/45/9b/5fb899d41a0f8d927c64f126794bc312.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/8c/a8/09b97e025f344d0e0d05245926f65ba6.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b0/fd/be/68e480053bf68493232c75df86b66978.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/90/73/99/0db8369e7873ef63ad813e9b81ddd5d2.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6c/75/d9/6da0b65232beac5e3b73274eabd1a6ec.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/14/2c/31fa634784e91004778549ee9f7915a9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/b7/8b/7bd87c7e4ce32d719b9a55391d746ad7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/4f/c1/f6e0f64980bc4f9cd51a23eba78c3cba.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ec/42/56/cb83392c7e5091d9faeca52cd29348c5.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a7/ae/3a/d7aaa7c0bae2a1059d79e9d7870006af.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3f/a6/a4/140ce4c6780c706edcfdcabcf61950b0.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/media/catalog/producttmp/5d/f8/b9/8a014046b6dff053e26820da02169d2a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/a8/e0/0fabf09e71ac203abefa2d19dc473ca7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/db/b5/11/9b49a332d68f5f3e77ba0cd203e4da60.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/89/5f/7b/77661c5bc169a60097c58e905ea983cd.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/37/82/71029b2714d170637fa91f08e1a1f3d3.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/db/04/51/15118c245e9f3cf36c718c7c2dc5a933.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/01/95/f8/ecb35729e900d174cdfb60e63cdc91fd.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/04/cb/33/731cc5c338a591a42275106a1dc72986.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/d2/5b/91bbb30a1a3e470617f7fad6480bcea7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/7f/b2/59de1aa6769a04980bf32166ccc700d8.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/f2/92/10fd7166684ce40596f2ffbe980a9ced.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c6/14/17/90c3d86839f01d3788cf51bdc1dc51e9.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/29/d3/ff/c375a5143579ff61d25375e3e55f5a2a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cf/11/26/4cf197a9f7f3fb0fa8b19b4256007c06.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/14/8c/81/fb9e28fb39287ef103ee0e9765f98564.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6d/fc/25/42afb0c0cf52cf8f83a0f98d5e550ff7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/a7/5a/bc0d48d4659e0d2bb24b9920e737a018.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/34/b4/006756d8e30705198fe156e235689321.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/1f/bc/fa056b1e5f54c36042b2755a642f11f4.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/32/4b/73/cdfc830c5891013ed6af5c8be68b97cc.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/75/e9/6cdaf46eac4a98bce8ac4e6e6d1c1a60.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/35/cb/84/790b48c73b35378a391c011cf9fd5681.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d6/e6/f1/1a44b1539f5465cc5b28b699d74adbd5.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/0c/5f/ae65a4730ba203032beef5cdc6c959f8.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6f/66/9b/e8d51754d73efdb5901536e4262d644b.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/2a/28/29/3daa0a5be1e12eeff9d5295da94e42d9.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/78/9c/37/5699ccee6cd1d7b5b68bff00b80dc608.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/71/99/3f/84fb391986c91682a94334304e844856.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/6a/da/ae/cceb0332cd470a4390b34259137fc374.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/65/83/e1/43688269800cd87d7b13b2fc04bd7a4a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/65/eb/8f/605a790fe74b2edc8b97373c955f0674.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/48/af/8e/531b253dc6c4129b7347d9c1635c200d.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/2e/ed/35/0f83fbe0583f484f7079dde894fce6ac.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/19/e2/f5b790ba517f48f43f88f711a93ba492.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/53/2f/9f/bfecd76a1ebfe0b7657dc2fe74079fd8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/49/de/6c/eff4593d00ec470babc53f8647457e0f.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ce/84/c7/93187b7ae7acededa100e6cc02e79828.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/74/aa/bc/5a87679708539a7edf488f20ac9e5c58.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/3b/f6/e9/af3add978120e7f1fa143af0fbd52e33.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/3c/75/71/848e43b9655e2ebf46d470b175a8aa29.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/89/09/1a/2f279301e492a813f79570dda97f3231.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/08/76/a5/de3fb3d1d1fc711156c60fb4616a2f63.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4a/f7/24/ecf0a4bd65cd2e9af8d959b8d44cd890.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/8b/28/d5/52a69fbfa364ddf143e5d283b5be1011.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/80/be/2f/78fe966f420d3c69eff19883d1a33df0.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/17/4c/f8/4845fd322e80b270b7f1a21f9b65da76.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0b/b5/88/7a745e1be60d35000868ec8e99ab96ae.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ac/ed/15/c7847e98527242dba0721bbb18cfeb8c.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/80/b6/d5/0fc8e6d3288e2aa31d1796f4993f6186.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7c/c9/3b/86cef58040c45f2db92fb288277627af.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6a/29/36/d40ee148944540cb05b639a48945ce03.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/87/4f/2d/422aae6f11c77595e6762d7758c8414e.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/41/ef/09/1856c31e2c452bbeac12f85a218c4bce.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e6/24/b2/2e370c77354265867449415018c9844c.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/c2/71/0218ffcde5582b38502c8a2f5ebad629.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8d/f0/57/04ece7be81852bc9e61ad3fe507120ab.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/e6/64/ed77e9ad050ebd69fd067036166b3d8d.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/d2/5b/91bbb30a1a3e470617f7fad6480bcea7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/7f/b2/59de1aa6769a04980bf32166ccc700d8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1c/21/4a/053e334128c91eee2a58c52412504d14.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/01/08/6d/7a5797d6c8a330917cb92d357a681951.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/f2/92/10fd7166684ce40596f2ffbe980a9ced.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c6/14/17/90c3d86839f01d3788cf51bdc1dc51e9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f8/ed/56/3543b5de6625c4b4f4749b519be210ff.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bf/0e/a9/62280749cd095d6dd351c8e01d2b7365.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/29/d3/ff/c375a5143579ff61d25375e3e55f5a2a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/2e/65/61/62692ccf5b7db3bdabd8aa437f0f7298.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6d/fc/25/42afb0c0cf52cf8f83a0f98d5e550ff7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/a7/5a/bc0d48d4659e0d2bb24b9920e737a018.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/34/b4/006756d8e30705198fe156e235689321.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/1f/bc/fa056b1e5f54c36042b2755a642f11f4.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/75/e9/6cdaf46eac4a98bce8ac4e6e6d1c1a60.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/35/cb/84/790b48c73b35378a391c011cf9fd5681.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c9/54/99/8b1432ffee329875e76d6cdb42ebaa4a.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d6/e6/f1/1a44b1539f5465cc5b28b699d74adbd5.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/0c/5f/ae65a4730ba203032beef5cdc6c959f8.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6f/66/9b/e8d51754d73efdb5901536e4262d644b.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/2a/28/29/3daa0a5be1e12eeff9d5295da94e42d9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/71/99/3f/84fb391986c91682a94334304e844856.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7c/c9/3b/86cef58040c45f2db92fb288277627af.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6a/29/36/d40ee148944540cb05b639a48945ce03.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ab/94/3d/33bd002169659e6530b6b347693968e8.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a9/02/56/489ddd7ae5d52b0f52b1fbf5bd6b21cf.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f7/91/c0/18d4091d0d0a24585bde2c3a4c3300d7.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c5/3b/92/8d3c192d0e2f9665571a8646f7b33849.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/75/e9/0acd44a8cb5ccad0585b27fd392f431b.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/be/f8/1c/0d92c40b96908d1bb98fcd1a9d6733b0.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/48/fe/f7/af958518c1e69b92ca76f08e6f084407.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/7f/b2/ceb645876870d6fc2c59ccecdca571ed.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/75/e9/4be6f57ca7bc16a58683def0c792ec27.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9c/18/51/5a7a88a6c7d10f751a9979dc182f7c0f.jpg</t>
   </si>
   <si>
     <t>Laptop - Máy Vi Tính - Linh kiện</t>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>278226869</v>
+        <v>278226504</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>278226504</v>
+        <v>278078286</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>278078317</v>
+        <v>278078281</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>278078298</v>
+        <v>278076611</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>278078286</v>
+        <v>278071899</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>278078281</v>
+        <v>277991695</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>278078278</v>
+        <v>277961929</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>278076611</v>
+        <v>277953961</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>278076601</v>
+        <v>277936690</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>278071899</v>
+        <v>277451016</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>277991695</v>
+        <v>277363552</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>277912853</v>
+        <v>277361314</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>277451016</v>
+        <v>276378910</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>277363552</v>
+        <v>276365829</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>277361314</v>
+        <v>275854386</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>276378910</v>
+        <v>275382480</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>276370396</v>
+        <v>275288865</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>276366370</v>
+        <v>275269577</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>276366073</v>
+        <v>274643985</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>275854386</v>
+        <v>273949286</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>275382480</v>
+        <v>273747303</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
@@ -1681,7 +1681,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>275269577</v>
+        <v>273679076</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>274643985</v>
+        <v>273309458</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>274419342</v>
+        <v>273187662</v>
       </c>
       <c r="B25" t="s">
         <v>28</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>274378954</v>
+        <v>273186974</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>273949286</v>
+        <v>273002756</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>272828266</v>
+        <v>271264846</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>252566514</v>
+        <v>270837635</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>248830867</v>
+        <v>252566514</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>247666447</v>
+        <v>248830867</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>247656002</v>
+        <v>225195616</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>225195616</v>
+        <v>225195387</v>
       </c>
       <c r="B33" t="s">
         <v>36</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>225195387</v>
+        <v>222707075</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>278078311</v>
+        <v>278226869</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>278076593</v>
+        <v>278078317</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>277912740</v>
+        <v>277961884</v>
       </c>
       <c r="B45" t="s">
         <v>48</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>277912721</v>
+        <v>277952237</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>277912717</v>
+        <v>277945130</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>277912715</v>
+        <v>277937199</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>277672516</v>
+        <v>277936146</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>277466579</v>
+        <v>277912853</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>277462473</v>
+        <v>277912740</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>277446629</v>
+        <v>277912721</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>277363548</v>
+        <v>277912715</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>277361271</v>
+        <v>277908157</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>276603695</v>
+        <v>277672516</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>276366329</v>
+        <v>277466579</v>
       </c>
       <c r="B56" t="s">
         <v>59</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>276366221</v>
+        <v>277446629</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>276366080</v>
+        <v>276603695</v>
       </c>
       <c r="B58" t="s">
         <v>61</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>276365829</v>
+        <v>276366370</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>275854376</v>
+        <v>276366329</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>275850110</v>
+        <v>276026379</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>275746519</v>
+        <v>275854376</v>
       </c>
       <c r="B62" t="s">
         <v>65</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>275721993</v>
+        <v>275850110</v>
       </c>
       <c r="B63" t="s">
         <v>66</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>275382529</v>
+        <v>275154280</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>275154280</v>
+        <v>274734984</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
@@ -2412,7 +2412,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>273647623</v>
+        <v>274378954</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>273231142</v>
+        <v>273747677</v>
       </c>
       <c r="B67" t="s">
         <v>70</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>252566338</v>
+        <v>273679080</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>225934432</v>
+        <v>273329318</v>
       </c>
       <c r="B69" t="s">
         <v>72</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>225363237</v>
+        <v>253096916</v>
       </c>
       <c r="B70" t="s">
         <v>73</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>214863401</v>
+        <v>252566338</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>214863371</v>
+        <v>225934432</v>
       </c>
       <c r="B72" t="s">
         <v>75</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>214863351</v>
+        <v>214863371</v>
       </c>
       <c r="B73" t="s">
         <v>76</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>198437064</v>
+        <v>214863351</v>
       </c>
       <c r="B74" t="s">
         <v>77</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>189572223</v>
+        <v>189572199</v>
       </c>
       <c r="B75" t="s">
         <v>78</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>189572199</v>
+        <v>186272654</v>
       </c>
       <c r="B76" t="s">
         <v>79</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>160445997</v>
+        <v>183743642</v>
       </c>
       <c r="B77" t="s">
         <v>80</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>278454662</v>
+        <v>278588312</v>
       </c>
       <c r="B82" t="s">
         <v>85</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>278304793</v>
+        <v>278454662</v>
       </c>
       <c r="B83" t="s">
         <v>86</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>278304363</v>
+        <v>278304793</v>
       </c>
       <c r="B84" t="s">
         <v>87</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>278076596</v>
+        <v>278078311</v>
       </c>
       <c r="B89" t="s">
         <v>92</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>275852844</v>
+        <v>278076596</v>
       </c>
       <c r="B90" t="s">
         <v>93</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>275850187</v>
+        <v>278076593</v>
       </c>
       <c r="B91" t="s">
         <v>94</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>275516477</v>
+        <v>277937155</v>
       </c>
       <c r="B92" t="s">
         <v>95</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>275381290</v>
+        <v>277912717</v>
       </c>
       <c r="B93" t="s">
         <v>96</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>274775419</v>
+        <v>277363548</v>
       </c>
       <c r="B94" t="s">
         <v>97</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>273634022</v>
+        <v>277361271</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>273239856</v>
+        <v>277274848</v>
       </c>
       <c r="B96" t="s">
         <v>99</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>271949876</v>
+        <v>276366221</v>
       </c>
       <c r="B97" t="s">
         <v>100</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>247667322</v>
+        <v>276026443</v>
       </c>
       <c r="B98" t="s">
         <v>101</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>225940640</v>
+        <v>275852844</v>
       </c>
       <c r="B99" t="s">
         <v>102</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>205305968</v>
+        <v>275850187</v>
       </c>
       <c r="B100" t="s">
         <v>103</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>205303070</v>
+        <v>275746519</v>
       </c>
       <c r="B101" t="s">
         <v>104</v>
